--- a/src/assets/projets/Projet_additive_CLC_CLSB_Solution_additive_delice.xlsx
+++ b/src/assets/projets/Projet_additive_CLC_CLSB_Solution_additive_delice.xlsx
@@ -461,10 +461,10 @@
         <v>EN_COURS</v>
       </c>
       <c r="G2">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="H2">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -546,7 +546,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E21"/>
+  <dimension ref="A1:E20"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -579,7 +579,7 @@
         <v>8</v>
       </c>
       <c r="E2">
-        <v>9561</v>
+        <v>95671.24</v>
       </c>
     </row>
     <row r="3">
@@ -771,24 +771,24 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>STE S.C.P.E</v>
+        <v>BYMS</v>
       </c>
       <c r="B14" t="str">
-        <v xml:space="preserve">Matériel </v>
+        <v xml:space="preserve">matériel </v>
       </c>
       <c r="C14" t="str">
         <v/>
       </c>
       <c r="D14" t="str">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E14">
-        <v>5893.445</v>
+        <v>413.338</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>BYMS</v>
+        <v>AMF INDUSTRIELLE</v>
       </c>
       <c r="B15" t="str">
         <v xml:space="preserve">matériel </v>
@@ -797,124 +797,107 @@
         <v/>
       </c>
       <c r="D15" t="str">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="E15">
-        <v>413.338</v>
+        <v>15946</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>AMF INDUSTRIELLE</v>
+        <v>AMEL</v>
       </c>
       <c r="B16" t="str">
-        <v xml:space="preserve">matériel </v>
+        <v xml:space="preserve">COFFRET </v>
       </c>
       <c r="C16" t="str">
         <v/>
       </c>
       <c r="D16" t="str">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E16">
-        <v>15946</v>
+        <v>14673.95</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>AMEL</v>
+        <v>BIAS</v>
       </c>
       <c r="B17" t="str">
-        <v xml:space="preserve">COFFRET </v>
+        <v>matériel</v>
       </c>
       <c r="C17" t="str">
         <v/>
       </c>
       <c r="D17" t="str">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E17">
-        <v>14673.95</v>
+        <v>10302.96</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>BIAS</v>
+        <v>MAISON INOX</v>
       </c>
       <c r="B18" t="str">
-        <v>matériel</v>
+        <v xml:space="preserve">MATERIEL </v>
       </c>
       <c r="C18" t="str">
         <v/>
       </c>
       <c r="D18" t="str">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E18">
-        <v>6462.8</v>
+        <v>30828.096</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>MAISON INOX</v>
+        <v>MAISION INOX</v>
       </c>
       <c r="B19" t="str">
-        <v xml:space="preserve">MATERIEL </v>
+        <v xml:space="preserve">MATRIEL INOX </v>
       </c>
       <c r="C19" t="str">
         <v/>
       </c>
       <c r="D19" t="str">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="E19">
-        <v>30828.096</v>
+        <v>3619.997</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>MAISION INOX</v>
+        <v>UNIVERS AUTOMATISME</v>
       </c>
       <c r="B20" t="str">
-        <v xml:space="preserve">MATRIEL INOX </v>
+        <v xml:space="preserve">matériel </v>
       </c>
       <c r="C20" t="str">
         <v/>
       </c>
       <c r="D20" t="str">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E20">
-        <v>3619.997</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="str">
-        <v>UNIVERS AUTOMATISME</v>
-      </c>
-      <c r="B21" t="str">
-        <v xml:space="preserve">matériel </v>
-      </c>
-      <c r="C21" t="str">
-        <v/>
-      </c>
-      <c r="D21" t="str">
-        <v>31</v>
-      </c>
-      <c r="E21">
         <v>579.599</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E21"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E20"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:D3"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -932,21 +915,35 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>test</v>
+        <v xml:space="preserve">steg et sonede </v>
       </c>
       <c r="B2" t="str">
-        <v>test</v>
+        <v>charge</v>
       </c>
       <c r="C2">
-        <v>200</v>
+        <v>3000</v>
       </c>
       <c r="D2" t="str">
-        <v/>
+        <v>2026-09-08</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v xml:space="preserve">ménage </v>
+      </c>
+      <c r="B3" t="str">
+        <v xml:space="preserve">charge femme de ménage </v>
+      </c>
+      <c r="C3">
+        <v>3000</v>
+      </c>
+      <c r="D3" t="str">
+        <v>2026-09-08</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D3"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -963,7 +960,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:E15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1097,16 +1094,100 @@
         <v xml:space="preserve">deplacement sidi bouzid: prise des notes </v>
       </c>
     </row>
+    <row r="10">
+      <c r="B10" t="str">
+        <v xml:space="preserve">déplacement </v>
+      </c>
+      <c r="C10" t="str">
+        <v>2026-07-08</v>
+      </c>
+      <c r="D10">
+        <v>100</v>
+      </c>
+      <c r="E10" t="str">
+        <v xml:space="preserve">déplacement cuve omar </v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" t="str">
+        <v xml:space="preserve">déplacement </v>
+      </c>
+      <c r="C11" t="str">
+        <v>2026-07-30</v>
+      </c>
+      <c r="D11">
+        <v>100</v>
+      </c>
+      <c r="E11" t="str">
+        <v xml:space="preserve">déplacement cuve omar </v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" t="str">
+        <v>déplacement</v>
+      </c>
+      <c r="C12" t="str">
+        <v>2026-08-10</v>
+      </c>
+      <c r="D12">
+        <v>100</v>
+      </c>
+      <c r="E12" t="str">
+        <v xml:space="preserve">déplacement cuve omar </v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" t="str">
+        <v>déplacement</v>
+      </c>
+      <c r="C13" t="str">
+        <v>2026-08-17</v>
+      </c>
+      <c r="D13">
+        <v>100</v>
+      </c>
+      <c r="E13" t="str">
+        <v xml:space="preserve">déplacement cuve omar </v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" t="str">
+        <v>déplacement</v>
+      </c>
+      <c r="C14" t="str">
+        <v>2026-08-29</v>
+      </c>
+      <c r="D14">
+        <v>100</v>
+      </c>
+      <c r="E14" t="str">
+        <v xml:space="preserve">déplacement cuve omar </v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" t="str">
+        <v>déplacement</v>
+      </c>
+      <c r="C15" t="str">
+        <v>2026-09-05</v>
+      </c>
+      <c r="D15">
+        <v>100</v>
+      </c>
+      <c r="E15" t="str">
+        <v xml:space="preserve">déplacement cuve omar </v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E9"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E15"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F8"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1162,7 +1243,7 @@
         <v>6000</v>
       </c>
       <c r="F3" t="str">
-        <v xml:space="preserve">développement </v>
+        <v xml:space="preserve">développement &amp; chef des équipe </v>
       </c>
     </row>
     <row r="4">
@@ -1233,152 +1314,548 @@
         <v>achat</v>
       </c>
     </row>
+    <row r="8">
+      <c r="B8" t="str">
+        <v>sms2i</v>
+      </c>
+      <c r="C8" t="str">
+        <v>180</v>
+      </c>
+      <c r="D8">
+        <v>200</v>
+      </c>
+      <c r="E8">
+        <v>36000</v>
+      </c>
+      <c r="F8" t="str">
+        <v xml:space="preserve">gérante </v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F7"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F8"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:E32"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
         <v>id</v>
       </c>
       <c r="B1" t="str">
+        <v>fournisseur</v>
+      </c>
+      <c r="C1" t="str">
+        <v>date</v>
+      </c>
+      <c r="D1" t="str">
+        <v>etat</v>
+      </c>
+      <c r="E1" t="str">
         <v>montant</v>
-      </c>
-      <c r="C1" t="str">
-        <v>fournisseur</v>
-      </c>
-      <c r="D1" t="str">
-        <v>date</v>
-      </c>
-      <c r="E1" t="str">
-        <v>etat</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>PRJ-1788506157358</v>
-      </c>
-      <c r="B2">
-        <v>28796.12</v>
+        <v>PAY-1788958252047-1</v>
+      </c>
+      <c r="B2" t="str">
+        <v>ASAM ENGINEERING</v>
       </c>
       <c r="C2" t="str">
-        <v xml:space="preserve">SIMS </v>
+        <v>2026-11-29</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-09-04</v>
-      </c>
-      <c r="E2" t="str">
+        <v>NON_PAYE</v>
+      </c>
+      <c r="E2">
+        <v>14280</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>PAY-1788958329223-1</v>
+      </c>
+      <c r="B3" t="str">
+        <v>SIMS</v>
+      </c>
+      <c r="C3" t="str">
+        <v>2026-07-15</v>
+      </c>
+      <c r="D3" t="str">
         <v>PAYE</v>
       </c>
-    </row>
-    <row r="3">
-      <c r="B3">
-        <v>28632.9</v>
-      </c>
-      <c r="C3" t="str">
-        <v xml:space="preserve">TUNISIE INOX </v>
-      </c>
-      <c r="D3" t="str">
-        <v>2026-09-04</v>
-      </c>
-      <c r="E3" t="str">
+      <c r="E3">
+        <v>28701.37</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>PAY-1788958329223-2</v>
+      </c>
+      <c r="B4" t="str">
+        <v>SIMS</v>
+      </c>
+      <c r="C4" t="str">
+        <v>2026-11-29</v>
+      </c>
+      <c r="D4" t="str">
+        <v>NON_PAYE</v>
+      </c>
+      <c r="E4">
+        <v>19134.25</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>PAY-1788958329223-3</v>
+      </c>
+      <c r="B5" t="str">
+        <v>SIMS</v>
+      </c>
+      <c r="C5" t="str">
+        <v>2026-12-29</v>
+      </c>
+      <c r="D5" t="str">
+        <v>NON_PAYE</v>
+      </c>
+      <c r="E5">
+        <v>47835.62</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>PAY-1788959073144-1</v>
+      </c>
+      <c r="B6" t="str">
+        <v>TUNISIE INOX</v>
+      </c>
+      <c r="C6" t="str">
+        <v>2026-08-06</v>
+      </c>
+      <c r="D6" t="str">
         <v>PAYE</v>
       </c>
-    </row>
-    <row r="4">
-      <c r="B4">
-        <v>28060.272</v>
-      </c>
-      <c r="C4" t="str">
-        <v xml:space="preserve">TUNISIE INOX </v>
-      </c>
-      <c r="D4" t="str">
-        <v>2026-09-04</v>
-      </c>
-      <c r="E4" t="str">
+      <c r="E6">
+        <v>57262.8</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>PAY-1788959073144-2</v>
+      </c>
+      <c r="B7" t="str">
+        <v>TUNISIE INOX</v>
+      </c>
+      <c r="C7" t="str">
+        <v>2026-10-01</v>
+      </c>
+      <c r="D7" t="str">
+        <v>NON_PAYE</v>
+      </c>
+      <c r="E7">
+        <v>38175.2</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>PAY-1788959073144-3</v>
+      </c>
+      <c r="B8" t="str">
+        <v>TUNISIE INOX</v>
+      </c>
+      <c r="C8" t="str">
+        <v>2026-11-01</v>
+      </c>
+      <c r="D8" t="str">
+        <v>NON_PAYE</v>
+      </c>
+      <c r="E8">
+        <v>95438</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>PAY-1788959233968-1</v>
+      </c>
+      <c r="B9" t="str">
+        <v>TSS TECHNO-SOLUTIONS &amp; SERVICES</v>
+      </c>
+      <c r="C9" t="str">
+        <v>2026-09-30</v>
+      </c>
+      <c r="D9" t="str">
         <v>PAYE</v>
       </c>
-    </row>
-    <row r="5">
-      <c r="B5">
-        <v>4672.591</v>
-      </c>
-      <c r="C5" t="str">
-        <v>equipement moderne ( variateur danfoss)</v>
-      </c>
-      <c r="D5" t="str">
-        <v>2026-09-04</v>
-      </c>
-      <c r="E5" t="str">
+      <c r="E9">
+        <v>11481.12</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>PAY-1788959233968-2</v>
+      </c>
+      <c r="B10" t="str">
+        <v>TSS TECHNO-SOLUTIONS &amp; SERVICES</v>
+      </c>
+      <c r="C10" t="str">
+        <v>2026-11-01</v>
+      </c>
+      <c r="D10" t="str">
+        <v>NON_PAYE</v>
+      </c>
+      <c r="E10">
+        <v>26789.27</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>PAY-1788959482024-1</v>
+      </c>
+      <c r="B11" t="str">
+        <v>JETS</v>
+      </c>
+      <c r="C11" t="str">
+        <v>2026-07-31</v>
+      </c>
+      <c r="D11" t="str">
         <v>PAYE</v>
       </c>
-    </row>
-    <row r="6">
-      <c r="B6">
-        <v>3761.495</v>
-      </c>
-      <c r="C6" t="str">
-        <v xml:space="preserve">amf </v>
-      </c>
-      <c r="D6" t="str">
-        <v>2026-09-04</v>
-      </c>
-      <c r="E6" t="str">
+      <c r="E11">
+        <v>31534.41</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>PAY-1788959482024-2</v>
+      </c>
+      <c r="B12" t="str">
+        <v>JETS</v>
+      </c>
+      <c r="C12" t="str">
+        <v>2026-12-17</v>
+      </c>
+      <c r="D12" t="str">
+        <v>NON_PAYE</v>
+      </c>
+      <c r="E12">
+        <v>62280.459</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" t="str">
+        <v>JETS</v>
+      </c>
+      <c r="C13" t="str">
+        <v>2026-12-17</v>
+      </c>
+      <c r="D13" t="str">
+        <v>NON_PAYE</v>
+      </c>
+      <c r="E13">
+        <v>62280.459</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>PAY-1788959849633-1</v>
+      </c>
+      <c r="B14" t="str">
+        <v>TECHNOPREST</v>
+      </c>
+      <c r="C14" t="str">
+        <v>2026-11-26</v>
+      </c>
+      <c r="D14" t="str">
+        <v>NON_PAYE</v>
+      </c>
+      <c r="E14">
+        <v>50323.82</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>PAY-1788959849633-2</v>
+      </c>
+      <c r="B15" t="str">
+        <v>TECHNOPREST</v>
+      </c>
+      <c r="C15" t="str">
+        <v>2026-09-10</v>
+      </c>
+      <c r="D15" t="str">
+        <v>NON_PAYE</v>
+      </c>
+      <c r="E15">
+        <v>21147.441</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" t="str">
+        <v>MASTER MOTION</v>
+      </c>
+      <c r="C16" t="str">
+        <v>2026-12-30</v>
+      </c>
+      <c r="D16" t="str">
+        <v>NON_PAYE</v>
+      </c>
+      <c r="E16">
+        <v>22250.025</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" t="str">
+        <v>CONCEPTION DISTRIBUTION RÉALISATION</v>
+      </c>
+      <c r="C17" t="str">
+        <v>2026-12-15</v>
+      </c>
+      <c r="D17" t="str">
+        <v>NON_PAYE</v>
+      </c>
+      <c r="E17">
+        <v>21289.1</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>PAY-1788960332858-1</v>
+      </c>
+      <c r="B18" t="str">
+        <v>EQUIPEMENT MODERNE</v>
+      </c>
+      <c r="C18" t="str">
+        <v>2026-07-08</v>
+      </c>
+      <c r="D18" t="str">
         <v>PAYE</v>
       </c>
-    </row>
-    <row r="7">
-      <c r="B7">
-        <v>4736.262</v>
-      </c>
-      <c r="C7" t="str">
-        <v>amf</v>
-      </c>
-      <c r="D7" t="str">
-        <v>2026-09-04</v>
-      </c>
-      <c r="E7" t="str">
+      <c r="E18">
+        <v>4719.49</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>PAY-1788960332858-2</v>
+      </c>
+      <c r="B19" t="str">
+        <v>EQUIPEMENT MODERNE</v>
+      </c>
+      <c r="C19" t="str">
+        <v>2026-09-16</v>
+      </c>
+      <c r="D19" t="str">
+        <v>NON_PAYE</v>
+      </c>
+      <c r="E19">
+        <v>11012.13</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" t="str">
+        <v>CONCEPTION DISTRIBUTION RÉALISATION</v>
+      </c>
+      <c r="C20" t="str">
+        <v>2026-12-15</v>
+      </c>
+      <c r="D20" t="str">
+        <v>NON_PAYE</v>
+      </c>
+      <c r="E20">
+        <v>111360.2</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>PAY-1788961978871-1</v>
+      </c>
+      <c r="B21" t="str">
+        <v>GENERAL METAL</v>
+      </c>
+      <c r="C21" t="str">
+        <v>2026-08-06</v>
+      </c>
+      <c r="D21" t="str">
         <v>PAYE</v>
       </c>
-    </row>
-    <row r="8">
-      <c r="B8">
-        <v>1163.289</v>
-      </c>
-      <c r="C8" t="str">
-        <v>byms</v>
-      </c>
-      <c r="D8" t="str">
-        <v>2026-09-04</v>
-      </c>
-      <c r="E8" t="str">
+      <c r="E21">
+        <v>6636</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>PAY-1788961978871-2</v>
+      </c>
+      <c r="B22" t="str">
+        <v>GENERAL METAL</v>
+      </c>
+      <c r="C22" t="str">
+        <v>2026-10-01</v>
+      </c>
+      <c r="D22" t="str">
+        <v>NON_PAYE</v>
+      </c>
+      <c r="E22">
+        <v>6280.672</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" t="str">
+        <v>BYMS</v>
+      </c>
+      <c r="C23" t="str">
+        <v>2026-09-01</v>
+      </c>
+      <c r="D23" t="str">
         <v>PAYE</v>
       </c>
-    </row>
-    <row r="9">
-      <c r="B9">
-        <v>414.338</v>
-      </c>
-      <c r="C9" t="str">
-        <v>bums</v>
-      </c>
-      <c r="D9" t="str">
-        <v/>
-      </c>
-      <c r="E9" t="str">
+      <c r="E23">
+        <v>413.338</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" t="str">
+        <v>AMF INDUSTRIELLE</v>
+      </c>
+      <c r="C24" t="str">
+        <v>2026-09-23</v>
+      </c>
+      <c r="D24" t="str">
+        <v>NON_PAYE</v>
+      </c>
+      <c r="E24">
+        <v>11651.278</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" t="str">
+        <v>AMEL</v>
+      </c>
+      <c r="C25" t="str">
+        <v>2026-09-01</v>
+      </c>
+      <c r="D25" t="str">
         <v>PAYE</v>
+      </c>
+      <c r="E25">
+        <v>14673.95</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>PAY-1788962583498-1</v>
+      </c>
+      <c r="B26" t="str">
+        <v>SOCIETE BIAS</v>
+      </c>
+      <c r="C26" t="str">
+        <v>2026-07-23</v>
+      </c>
+      <c r="D26" t="str">
+        <v>PAYE</v>
+      </c>
+      <c r="E26">
+        <v>2585.12</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v>PAY-1788962583498-2</v>
+      </c>
+      <c r="B27" t="str">
+        <v>SOCIETE BIAS</v>
+      </c>
+      <c r="C27" t="str">
+        <v>2026-08-26</v>
+      </c>
+      <c r="D27" t="str">
+        <v>NON_PAYE</v>
+      </c>
+      <c r="E27">
+        <v>1938.84</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>PAY-1788962583498-3</v>
+      </c>
+      <c r="B28" t="str">
+        <v>SOCIETE BIAS</v>
+      </c>
+      <c r="C28" t="str">
+        <v>2026-09-26</v>
+      </c>
+      <c r="D28" t="str">
+        <v>NON_PAYE</v>
+      </c>
+      <c r="E28">
+        <v>1938.84</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" t="str">
+        <v>UNIVERS AUTOMATISME</v>
+      </c>
+      <c r="C29" t="str">
+        <v>2026-09-09</v>
+      </c>
+      <c r="D29" t="str">
+        <v>PAYE</v>
+      </c>
+      <c r="E29">
+        <v>579.599</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" t="str">
+        <v>LA MAISON DE L'INOX</v>
+      </c>
+      <c r="C30" t="str">
+        <v>2026-08-31</v>
+      </c>
+      <c r="D30" t="str">
+        <v>PAYE</v>
+      </c>
+      <c r="E30">
+        <v>34448.093</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" t="str">
+        <v>SOCIETE BIAS</v>
+      </c>
+      <c r="C31" t="str">
+        <v>2026-08-06</v>
+      </c>
+      <c r="D31" t="str">
+        <v>PAYE</v>
+      </c>
+      <c r="E31">
+        <v>3801.768</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" t="str">
+        <v>AMF INDUSTRIELLE</v>
+      </c>
+      <c r="C32" t="str">
+        <v>2026-07-23</v>
+      </c>
+      <c r="D32" t="str">
+        <v>PAYE</v>
+      </c>
+      <c r="E32">
+        <v>4763</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E9"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E32"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -1711,7 +2188,7 @@
         <v xml:space="preserve">câblage </v>
       </c>
       <c r="D4">
-        <v>20000</v>
+        <v>3000</v>
       </c>
     </row>
   </sheetData>

--- a/src/assets/projets/Projet_additive_CLC_CLSB_Solution_additive_delice.xlsx
+++ b/src/assets/projets/Projet_additive_CLC_CLSB_Solution_additive_delice.xlsx
@@ -461,10 +461,10 @@
         <v>EN_COURS</v>
       </c>
       <c r="G2">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="H2">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -960,7 +960,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E15"/>
+  <dimension ref="A1:E16"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1102,7 +1102,7 @@
         <v>2026-07-08</v>
       </c>
       <c r="D10">
-        <v>100</v>
+        <v>140</v>
       </c>
       <c r="E10" t="str">
         <v xml:space="preserve">déplacement cuve omar </v>
@@ -1116,7 +1116,7 @@
         <v>2026-07-30</v>
       </c>
       <c r="D11">
-        <v>100</v>
+        <v>140</v>
       </c>
       <c r="E11" t="str">
         <v xml:space="preserve">déplacement cuve omar </v>
@@ -1130,7 +1130,7 @@
         <v>2026-08-10</v>
       </c>
       <c r="D12">
-        <v>100</v>
+        <v>140</v>
       </c>
       <c r="E12" t="str">
         <v xml:space="preserve">déplacement cuve omar </v>
@@ -1144,7 +1144,7 @@
         <v>2026-08-17</v>
       </c>
       <c r="D13">
-        <v>100</v>
+        <v>140</v>
       </c>
       <c r="E13" t="str">
         <v xml:space="preserve">déplacement cuve omar </v>
@@ -1158,7 +1158,7 @@
         <v>2026-08-29</v>
       </c>
       <c r="D14">
-        <v>100</v>
+        <v>140</v>
       </c>
       <c r="E14" t="str">
         <v xml:space="preserve">déplacement cuve omar </v>
@@ -1172,22 +1172,36 @@
         <v>2026-09-05</v>
       </c>
       <c r="D15">
-        <v>100</v>
+        <v>140</v>
       </c>
       <c r="E15" t="str">
         <v xml:space="preserve">déplacement cuve omar </v>
       </c>
     </row>
+    <row r="16">
+      <c r="B16" t="str">
+        <v xml:space="preserve">déplacement </v>
+      </c>
+      <c r="C16" t="str">
+        <v>2026-09-11</v>
+      </c>
+      <c r="D16">
+        <v>140</v>
+      </c>
+      <c r="E16" t="str">
+        <v>déplacement cuve omar</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E15"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E16"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:F7"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1217,13 +1231,13 @@
         <v xml:space="preserve">rafik </v>
       </c>
       <c r="C2" t="str">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D2">
         <v>101</v>
       </c>
       <c r="E2">
-        <v>1313</v>
+        <v>1515</v>
       </c>
       <c r="F2" t="str">
         <v xml:space="preserve">développement </v>
@@ -1314,26 +1328,9 @@
         <v>achat</v>
       </c>
     </row>
-    <row r="8">
-      <c r="B8" t="str">
-        <v>sms2i</v>
-      </c>
-      <c r="C8" t="str">
-        <v>180</v>
-      </c>
-      <c r="D8">
-        <v>200</v>
-      </c>
-      <c r="E8">
-        <v>36000</v>
-      </c>
-      <c r="F8" t="str">
-        <v xml:space="preserve">gérante </v>
-      </c>
-    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F8"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F7"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -1452,7 +1449,7 @@
         <v>TUNISIE INOX</v>
       </c>
       <c r="C7" t="str">
-        <v>2026-10-01</v>
+        <v>2026-12-21</v>
       </c>
       <c r="D7" t="str">
         <v>NON_PAYE</v>
@@ -1469,7 +1466,7 @@
         <v>TUNISIE INOX</v>
       </c>
       <c r="C8" t="str">
-        <v>2026-11-01</v>
+        <v>2027-01-21</v>
       </c>
       <c r="D8" t="str">
         <v>NON_PAYE</v>
@@ -1720,58 +1717,61 @@
     </row>
     <row r="24">
       <c r="B24" t="str">
-        <v>AMF INDUSTRIELLE</v>
+        <v>AMEL</v>
       </c>
       <c r="C24" t="str">
-        <v>2026-09-23</v>
+        <v>2026-09-01</v>
       </c>
       <c r="D24" t="str">
-        <v>NON_PAYE</v>
+        <v>PAYE</v>
       </c>
       <c r="E24">
-        <v>11651.278</v>
+        <v>14673.95</v>
       </c>
     </row>
     <row r="25">
+      <c r="A25" t="str">
+        <v>PAY-1788962583498-1</v>
+      </c>
       <c r="B25" t="str">
-        <v>AMEL</v>
+        <v>SOCIETE BIAS</v>
       </c>
       <c r="C25" t="str">
-        <v>2026-09-01</v>
+        <v>2026-07-23</v>
       </c>
       <c r="D25" t="str">
         <v>PAYE</v>
       </c>
       <c r="E25">
-        <v>14673.95</v>
+        <v>2585.12</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>PAY-1788962583498-1</v>
+        <v>PAY-1788962583498-2</v>
       </c>
       <c r="B26" t="str">
         <v>SOCIETE BIAS</v>
       </c>
       <c r="C26" t="str">
-        <v>2026-07-23</v>
+        <v>2026-08-26</v>
       </c>
       <c r="D26" t="str">
-        <v>PAYE</v>
+        <v>NON_PAYE</v>
       </c>
       <c r="E26">
-        <v>2585.12</v>
+        <v>1938.84</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>PAY-1788962583498-2</v>
+        <v>PAY-1788962583498-3</v>
       </c>
       <c r="B27" t="str">
         <v>SOCIETE BIAS</v>
       </c>
       <c r="C27" t="str">
-        <v>2026-08-26</v>
+        <v>2026-09-26</v>
       </c>
       <c r="D27" t="str">
         <v>NON_PAYE</v>
@@ -1781,62 +1781,59 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="str">
-        <v>PAY-1788962583498-3</v>
-      </c>
       <c r="B28" t="str">
-        <v>SOCIETE BIAS</v>
+        <v>UNIVERS AUTOMATISME</v>
       </c>
       <c r="C28" t="str">
-        <v>2026-09-26</v>
+        <v>2026-09-09</v>
       </c>
       <c r="D28" t="str">
-        <v>NON_PAYE</v>
+        <v>PAYE</v>
       </c>
       <c r="E28">
-        <v>1938.84</v>
+        <v>579.599</v>
       </c>
     </row>
     <row r="29">
       <c r="B29" t="str">
-        <v>UNIVERS AUTOMATISME</v>
+        <v>LA MAISON DE L'INOX</v>
       </c>
       <c r="C29" t="str">
-        <v>2026-09-09</v>
+        <v>2026-08-31</v>
       </c>
       <c r="D29" t="str">
         <v>PAYE</v>
       </c>
       <c r="E29">
-        <v>579.599</v>
+        <v>34448.093</v>
       </c>
     </row>
     <row r="30">
       <c r="B30" t="str">
-        <v>LA MAISON DE L'INOX</v>
+        <v>SOCIETE BIAS</v>
       </c>
       <c r="C30" t="str">
-        <v>2026-08-31</v>
+        <v>2026-08-06</v>
       </c>
       <c r="D30" t="str">
         <v>PAYE</v>
       </c>
       <c r="E30">
-        <v>34448.093</v>
+        <v>3801.768</v>
       </c>
     </row>
     <row r="31">
       <c r="B31" t="str">
-        <v>SOCIETE BIAS</v>
+        <v>AMF INDUSTRIELLE</v>
       </c>
       <c r="C31" t="str">
-        <v>2026-08-06</v>
+        <v>2026-09-11</v>
       </c>
       <c r="D31" t="str">
         <v>PAYE</v>
       </c>
       <c r="E31">
-        <v>3801.768</v>
+        <v>4763.262</v>
       </c>
     </row>
     <row r="32">
@@ -1844,13 +1841,13 @@
         <v>AMF INDUSTRIELLE</v>
       </c>
       <c r="C32" t="str">
-        <v>2026-07-23</v>
+        <v>2026-10-01</v>
       </c>
       <c r="D32" t="str">
-        <v>PAYE</v>
+        <v>NON_PAYE</v>
       </c>
       <c r="E32">
-        <v>4763</v>
+        <v>11051.278</v>
       </c>
     </row>
   </sheetData>
@@ -2017,7 +2014,7 @@
         <v/>
       </c>
       <c r="H6">
-        <v>20</v>
+        <v>32</v>
       </c>
     </row>
     <row r="7">
@@ -2157,7 +2154,7 @@
         <v>sadok</v>
       </c>
       <c r="C2" t="str">
-        <v>1Etude, dimensionnement, suivi et mise en service du Projet Station de dosage des</v>
+        <v>Etude, dimensionnement, suivi et mise en service du Projet Station de dosage des</v>
       </c>
       <c r="D2">
         <v>14280</v>
